--- a/data/exports/insurance_nghiem_thu.xlsx
+++ b/data/exports/insurance_nghiem_thu.xlsx
@@ -15,7 +15,8 @@
     <sheet name="cong_an_toan_von" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ngoai_le" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="universe" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="meta" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="danh_sach_theo_doi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="meta" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,6 +578,120 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-26T21:45:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>spec</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BA phản hồi IT tab Toàn ngành bảo hiểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eps_formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(EPS_t - EPS_t-4) / |EPS_t-4|, BA §2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0/3/7/10, BA §3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>score_version</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INS_TOAN_NGANH_50_V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eps_normalization_version</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EPS_STD_IAS33_DEDUP_V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>writes_to_db</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -630,7 +745,7 @@
     <col width="15" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="21" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="21" customWidth="1" min="45" max="45"/>
     <col width="17" customWidth="1" min="46" max="46"/>
     <col width="22" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -1094,6 +1209,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
         <v>254307973553</v>
       </c>
@@ -1295,6 +1415,11 @@
       <c r="AM3" t="n">
         <v>79</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
         <v>32898652621</v>
       </c>
@@ -1493,6 +1618,11 @@
           <t>VCSH giảm -1.8% YoY</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
         <v>12752606231</v>
       </c>
@@ -1691,6 +1821,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
         <v>540431850962</v>
       </c>
@@ -1897,6 +2032,11 @@
       <c r="AM6" t="n">
         <v>79</v>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
         <v>31604000429</v>
       </c>
@@ -2095,6 +2235,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
         <v>259786642077</v>
       </c>
@@ -2293,6 +2438,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
         <v>2824584416152</v>
       </c>
@@ -2491,6 +2641,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
         <v>324882597229</v>
       </c>
@@ -2689,6 +2844,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
         <v>245548590131</v>
       </c>
@@ -2887,6 +3047,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
         <v>239609896963</v>
       </c>
@@ -3085,6 +3250,11 @@
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
         <v>291456035820</v>
       </c>
@@ -3291,6 +3461,11 @@
       <c r="AM13" t="n">
         <v>79</v>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
         <v>1103154632356</v>
       </c>
@@ -3487,6 +3662,11 @@
       <c r="AL14" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -10016,7 +10196,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -10089,7 +10269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tổng điểm Toàn ngành</t>
+          <t>Điểm chung toàn ngành /50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10099,7 +10279,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tổng C1 đến C5, tối đa 50. Đây là điểm FA chung, KHÔNG phải điểm cuối cùng của doanh nghiệp bảo hiểm — 50 điểm chuyên sâu theo loại hình chưa triển khai.</t>
+          <t>Đây là điểm FA chung tối đa 50 điểm, chưa phải điểm FA cuối cùng. Điểm cuối cùng chỉ được hình thành sau khi cộng 50 điểm chuyên sâu theo loại hình.</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11315,6 +11495,9 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11348,6 +11531,21 @@
           <t>insurance_type</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ranked</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>watchlist_status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>watchlist_reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11380,6 +11578,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11412,6 +11613,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11444,6 +11648,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11476,6 +11683,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11508,6 +11718,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11540,6 +11753,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11572,11 +11788,14 @@
           <t>Holding/Hỗn hợp</t>
         </is>
       </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIG</t>
+          <t>IFA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11586,12 +11805,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bảo hiểm Quân đội</t>
+          <t>Bảo hiểm Viễn Đông</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HOSE</t>
+          <t>OTC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -11602,13 +11821,26 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chưa đủ lịch sử chấm điểm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Không có dữ liệu EPS chuẩn hóa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PGI</t>
+          <t>MIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11618,7 +11850,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bảo hiểm PJICO</t>
+          <t>Bảo hiểm Quân đội</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11635,12 +11867,15 @@
         <is>
           <t>Phi nhân thọ</t>
         </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRE</t>
+          <t>PGI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11650,29 +11885,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tái bảo hiểm PVI</t>
+          <t>Bảo hiểm PJICO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HNX</t>
+          <t>HOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tái bảo hiểm</t>
-        </is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11682,7 +11920,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bảo hiểm Bưu điện</t>
+          <t>Tái bảo hiểm PVI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11692,19 +11930,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Phi nhân thọ</t>
-        </is>
+          <t>Tái bảo hiểm</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PVI</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11714,7 +11955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PVI Holdings</t>
+          <t>Bảo hiểm Bưu điện</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11729,40 +11970,81 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Holding/Hỗn hợp</t>
-        </is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PVI Holdings</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HNX</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Holding/Hỗn hợp</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>VNR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>BH</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Tái bảo hiểm Quốc gia</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>HNX</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>8538</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Tái bảo hiểm</t>
         </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11776,106 +12058,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>ten</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loai_hinh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>san</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trang_thai</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ly_do</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated_at</t>
+          <t>IFA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26T20:40:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BA phản hồi IT tab Toàn ngành bảo hiểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>eps_formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>(EPS_t - EPS_t-4) / |EPS_t-4|, BA §2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>scale</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0/3/7/10, BA §3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>score_version</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INS_TOAN_NGANH_50_V1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>eps_normalization_version</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EPS_STD_IAS33_DEDUP_V2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>writes_to_db</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Bảo hiểm Viễn Đông</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chưa đủ lịch sử chấm điểm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Không có dữ liệu EPS chuẩn hóa</t>
         </is>
       </c>
     </row>

--- a/data/exports/insurance_nghiem_thu.xlsx
+++ b/data/exports/insurance_nghiem_thu.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26T21:45:47</t>
+          <t>2026-09-26T21:58:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/insurance_nghiem_thu.xlsx
+++ b/data/exports/insurance_nghiem_thu.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26T21:58:06</t>
+          <t>2026-09-26T22:17:54</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
     <col width="22" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
     <col width="21" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="36" customWidth="1" min="38" max="38"/>
     <col width="16" customWidth="1" min="39" max="39"/>
     <col width="21" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -15.9%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-15.9;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>VCSH giảm -1.8% YoY</t>
+          <t>EQUITY_DOWN:-1.8</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -11.0%</t>
+          <t>BUFFER_DOWN:-11.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -34.7%</t>
+          <t>BUFFER_DOWN:-34.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-25.3;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="AM16" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -14.0%</t>
+          <t>BUFFER_DOWN:-14.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -21.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-21.1;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="AM26" t="n">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-30.7;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="AM29" t="n">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -12.7%</t>
+          <t>BUFFER_DOWN:-12.7</t>
         </is>
       </c>
       <c r="AM36" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-18.1;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="AM39" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cảnh báo — đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>Cảnh báo — BUFFER_DOWN:-18.1;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cảnh báo — đệm vốn giảm -12.7%</t>
+          <t>Cảnh báo — BUFFER_DOWN:-12.7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Đạt — chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>Đạt — NO_WARNING</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Cảnh báo — đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>Cảnh báo — BUFFER_DOWN:-30.7;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10727,7 +10727,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-30.7;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -12.7%</t>
+          <t>BUFFER_DOWN:-12.7</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-18.1;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+          <t>BUFFER_DOWN:-25.3;GROWTH_GAP_2Q:20</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
+          <t>NO_WARNING</t>
         </is>
       </c>
     </row>
